--- a/results/table/18_sensortower_aei_country_share.xlsx
+++ b/results/table/18_sensortower_aei_country_share.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="1088">
   <si>
     <t>month</t>
   </si>
@@ -1163,6 +1163,822 @@
   </si>
   <si>
     <t>아르헨티</t>
+  </si>
+  <si>
+    <t>튀르키예</t>
+  </si>
+  <si>
+    <t>베트남</t>
+  </si>
+  <si>
+    <t>대만</t>
+  </si>
+  <si>
+    <t>iso2</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>VN</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>VN</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>VN</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>iso3</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>FRA</t>
+  </si>
+  <si>
+    <t>GBR</t>
+  </si>
+  <si>
+    <t>BRA</t>
+  </si>
+  <si>
+    <t>JPN</t>
+  </si>
+  <si>
+    <t>KOR</t>
+  </si>
+  <si>
+    <t>DEU</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>IDN</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>ITA</t>
+  </si>
+  <si>
+    <t>MEX</t>
+  </si>
+  <si>
+    <t>ARG</t>
+  </si>
+  <si>
+    <t>TUR</t>
+  </si>
+  <si>
+    <t>VNM</t>
+  </si>
+  <si>
+    <t>TWN</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>FRA</t>
+  </si>
+  <si>
+    <t>GBR</t>
+  </si>
+  <si>
+    <t>BRA</t>
+  </si>
+  <si>
+    <t>JPN</t>
+  </si>
+  <si>
+    <t>KOR</t>
+  </si>
+  <si>
+    <t>DEU</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>IDN</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>ITA</t>
+  </si>
+  <si>
+    <t>MEX</t>
+  </si>
+  <si>
+    <t>ARG</t>
+  </si>
+  <si>
+    <t>TUR</t>
+  </si>
+  <si>
+    <t>VNM</t>
+  </si>
+  <si>
+    <t>TWN</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>FRA</t>
+  </si>
+  <si>
+    <t>GBR</t>
+  </si>
+  <si>
+    <t>BRA</t>
+  </si>
+  <si>
+    <t>JPN</t>
+  </si>
+  <si>
+    <t>KOR</t>
+  </si>
+  <si>
+    <t>DEU</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>IDN</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>ITA</t>
+  </si>
+  <si>
+    <t>MEX</t>
+  </si>
+  <si>
+    <t>ARG</t>
+  </si>
+  <si>
+    <t>TUR</t>
+  </si>
+  <si>
+    <t>VNM</t>
+  </si>
+  <si>
+    <t>TWN</t>
+  </si>
+  <si>
+    <t>all_users</t>
+  </si>
+  <si>
+    <t>messages</t>
+  </si>
+  <si>
+    <t>claude_users</t>
+  </si>
+  <si>
+    <t>usage_pct</t>
+  </si>
+  <si>
+    <t>st_all_ww_pct</t>
+  </si>
+  <si>
+    <t>st_cl_ww_pct</t>
+  </si>
+  <si>
+    <t>st_all</t>
+  </si>
+  <si>
+    <t>st_cl</t>
+  </si>
+  <si>
+    <t>aei</t>
+  </si>
+  <si>
+    <t>r_aei_all</t>
+  </si>
+  <si>
+    <t>r_aei_cl</t>
+  </si>
+  <si>
+    <t>sig_work_pct</t>
+  </si>
+  <si>
+    <t>use_case_work_pct</t>
+  </si>
+  <si>
+    <t>work_messages</t>
+  </si>
+  <si>
+    <t>st_work</t>
+  </si>
+  <si>
+    <t>st_clwork</t>
+  </si>
+  <si>
+    <t>aei_work</t>
+  </si>
+  <si>
+    <t>stat</t>
+  </si>
+  <si>
+    <t>D:aei:st_all</t>
+  </si>
+  <si>
+    <t>D:aei:st_cl</t>
+  </si>
+  <si>
+    <t>D:aei_work:st_clwork</t>
+  </si>
+  <si>
+    <t>D:aei_work:st_work</t>
+  </si>
+  <si>
+    <t>D:use_case_work_pct:sig_work_pct</t>
+  </si>
+  <si>
+    <t>aei_work18</t>
+  </si>
+  <si>
+    <t>aei_work_pct_global</t>
+  </si>
+  <si>
+    <t>corr:aei:st_all</t>
+  </si>
+  <si>
+    <t>corr:aei:st_cl</t>
+  </si>
+  <si>
+    <t>corr:aei_work:st_clwork</t>
+  </si>
+  <si>
+    <t>corr:aei_work:st_work</t>
+  </si>
+  <si>
+    <t>corr:use_case_work_pct:sig_work_pct</t>
+  </si>
+  <si>
+    <t>cov_aei</t>
+  </si>
+  <si>
+    <t>cov_st_all</t>
+  </si>
+  <si>
+    <t>cov_st_cl</t>
+  </si>
+  <si>
+    <t>mdiff:aei:st_all</t>
+  </si>
+  <si>
+    <t>mdiff:aei:st_cl</t>
+  </si>
+  <si>
+    <t>mdiff:aei_work:st_clwork</t>
+  </si>
+  <si>
+    <t>mdiff:aei_work:st_work</t>
+  </si>
+  <si>
+    <t>mdiff:use_case_work_pct:sig_work_pct</t>
+  </si>
+  <si>
+    <t>sig_work18</t>
+  </si>
+  <si>
+    <t>sig_work_global</t>
+  </si>
+  <si>
+    <t>spear:aei:st_all</t>
+  </si>
+  <si>
+    <t>spear:aei:st_cl</t>
+  </si>
+  <si>
+    <t>spear:aei_work:st_clwork</t>
+  </si>
+  <si>
+    <t>spear:aei_work:st_work</t>
+  </si>
+  <si>
+    <t>spear:use_case_work_pct:sig_work_pct</t>
+  </si>
+  <si>
+    <t>vm202602</t>
+  </si>
+  <si>
+    <t>vm202604</t>
+  </si>
+  <si>
+    <t>vm202605</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>market</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Vietnam</t>
+  </si>
+  <si>
+    <t>Taiwan</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Vietnam</t>
+  </si>
+  <si>
+    <t>Taiwan</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Vietnam</t>
+  </si>
+  <si>
+    <t>Taiwan</t>
+  </si>
+  <si>
+    <t>kname</t>
+  </si>
+  <si>
+    <t>미국</t>
+  </si>
+  <si>
+    <t>인도</t>
+  </si>
+  <si>
+    <t>프랑스</t>
+  </si>
+  <si>
+    <t>영국</t>
+  </si>
+  <si>
+    <t>브라질</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>독일</t>
+  </si>
+  <si>
+    <t>호주</t>
+  </si>
+  <si>
+    <t>캐나다</t>
+  </si>
+  <si>
+    <t>인도네시아</t>
+  </si>
+  <si>
+    <t>스페인</t>
+  </si>
+  <si>
+    <t>이탈리아</t>
+  </si>
+  <si>
+    <t>멕시코</t>
+  </si>
+  <si>
+    <t>아르헨티나</t>
+  </si>
+  <si>
+    <t>튀르키예</t>
+  </si>
+  <si>
+    <t>베트남</t>
+  </si>
+  <si>
+    <t>대만</t>
+  </si>
+  <si>
+    <t>미국</t>
+  </si>
+  <si>
+    <t>인도</t>
+  </si>
+  <si>
+    <t>프랑스</t>
+  </si>
+  <si>
+    <t>영국</t>
+  </si>
+  <si>
+    <t>브라질</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>독일</t>
+  </si>
+  <si>
+    <t>호주</t>
+  </si>
+  <si>
+    <t>캐나다</t>
+  </si>
+  <si>
+    <t>인도네시아</t>
+  </si>
+  <si>
+    <t>스페인</t>
+  </si>
+  <si>
+    <t>이탈리아</t>
+  </si>
+  <si>
+    <t>멕시코</t>
+  </si>
+  <si>
+    <t>아르헨티나</t>
+  </si>
+  <si>
+    <t>튀르키예</t>
+  </si>
+  <si>
+    <t>베트남</t>
+  </si>
+  <si>
+    <t>대만</t>
+  </si>
+  <si>
+    <t>미국</t>
+  </si>
+  <si>
+    <t>인도</t>
+  </si>
+  <si>
+    <t>프랑스</t>
+  </si>
+  <si>
+    <t>영국</t>
+  </si>
+  <si>
+    <t>브라질</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>독일</t>
+  </si>
+  <si>
+    <t>호주</t>
+  </si>
+  <si>
+    <t>캐나다</t>
+  </si>
+  <si>
+    <t>인도네시아</t>
+  </si>
+  <si>
+    <t>스페인</t>
+  </si>
+  <si>
+    <t>이탈리아</t>
+  </si>
+  <si>
+    <t>멕시코</t>
+  </si>
+  <si>
+    <t>아르헨티나</t>
   </si>
   <si>
     <t>튀르키예</t>
@@ -2512,93 +3328,93 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>544</v>
+        <v>816</v>
       </c>
       <c r="B1" t="s">
-        <v>548</v>
+        <v>820</v>
       </c>
       <c r="C1" t="s">
-        <v>603</v>
+        <v>875</v>
       </c>
       <c r="D1" t="s">
-        <v>658</v>
+        <v>930</v>
       </c>
       <c r="E1" t="s">
-        <v>713</v>
+        <v>985</v>
       </c>
       <c r="F1" t="s">
-        <v>768</v>
+        <v>1040</v>
       </c>
       <c r="G1" t="s">
-        <v>769</v>
+        <v>1041</v>
       </c>
       <c r="H1" t="s">
-        <v>770</v>
+        <v>1042</v>
       </c>
       <c r="I1" t="s">
-        <v>771</v>
+        <v>1043</v>
       </c>
       <c r="J1" t="s">
-        <v>772</v>
+        <v>1044</v>
       </c>
       <c r="K1" t="s">
-        <v>773</v>
+        <v>1045</v>
       </c>
       <c r="L1" t="s">
-        <v>774</v>
+        <v>1046</v>
       </c>
       <c r="M1" t="s">
-        <v>775</v>
+        <v>1047</v>
       </c>
       <c r="N1" t="s">
-        <v>776</v>
+        <v>1048</v>
       </c>
       <c r="O1" t="s">
-        <v>777</v>
+        <v>1049</v>
       </c>
       <c r="P1" t="s">
-        <v>778</v>
+        <v>1050</v>
       </c>
       <c r="Q1" t="s">
-        <v>779</v>
+        <v>1051</v>
       </c>
       <c r="R1" t="s">
-        <v>780</v>
+        <v>1052</v>
       </c>
       <c r="S1" t="s">
-        <v>781</v>
+        <v>1053</v>
       </c>
       <c r="T1" t="s">
-        <v>782</v>
+        <v>1054</v>
       </c>
       <c r="U1" t="s">
-        <v>783</v>
+        <v>1055</v>
       </c>
       <c r="V1" t="s">
-        <v>784</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B2" t="s">
-        <v>549</v>
+        <v>821</v>
       </c>
       <c r="C2" t="s">
-        <v>604</v>
+        <v>876</v>
       </c>
       <c r="D2" t="s">
-        <v>659</v>
+        <v>931</v>
       </c>
       <c r="E2" t="s">
-        <v>714</v>
+        <v>986</v>
       </c>
       <c r="F2" s="1">
         <v>272680000</v>
       </c>
       <c r="G2" s="1">
-        <v>21867697614.256969</v>
+        <v>14656475711.788528</v>
       </c>
       <c r="H2" s="1">
         <v>22700000</v>
@@ -2613,7 +3429,7 @@
         <v>21.826923076923077</v>
       </c>
       <c r="L2" s="1">
-        <v>14.655660767782916</v>
+        <v>14.65566076778291</v>
       </c>
       <c r="M2" s="1">
         <v>23.924201384863466</v>
@@ -2622,7 +3438,7 @@
         <v>37.697709033332082</v>
       </c>
       <c r="O2" s="1">
-        <v>2.572228549135211</v>
+        <v>2.5722285491352119</v>
       </c>
       <c r="P2" s="1">
         <v>1.575714416832444</v>
@@ -2634,10 +3450,10 @@
         <v>40.415160182037305</v>
       </c>
       <c r="S2" s="1">
-        <v>7369414367.1151991</v>
+        <v>4939232496.5802917</v>
       </c>
       <c r="T2" s="1">
-        <v>15.141064782783589</v>
+        <v>15.141064782783593</v>
       </c>
       <c r="U2" s="1">
         <v>24.566387406534211</v>
@@ -2648,25 +3464,25 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B3" t="s">
-        <v>550</v>
+        <v>822</v>
       </c>
       <c r="C3" t="s">
-        <v>605</v>
+        <v>877</v>
       </c>
       <c r="D3" t="s">
-        <v>660</v>
+        <v>932</v>
       </c>
       <c r="E3" t="s">
-        <v>715</v>
+        <v>987</v>
       </c>
       <c r="F3" s="1">
         <v>618470000</v>
       </c>
       <c r="G3" s="1">
-        <v>49598485196.89566</v>
+        <v>33242594005.683773</v>
       </c>
       <c r="H3" s="1">
         <v>28300000</v>
@@ -2681,7 +3497,7 @@
         <v>27.21153846153846</v>
       </c>
       <c r="L3" s="1">
-        <v>33.240745617759643</v>
+        <v>33.240745617759636</v>
       </c>
       <c r="M3" s="1">
         <v>29.826207012847402</v>
@@ -2690,7 +3506,7 @@
         <v>10.447343706029342</v>
       </c>
       <c r="O3" s="1">
-        <v>0.31429330214685691</v>
+        <v>0.31429330214685697</v>
       </c>
       <c r="P3" s="1">
         <v>0.35027396214105372</v>
@@ -2702,10 +3518,10 @@
         <v>49.640579616077368</v>
       </c>
       <c r="S3" s="1">
-        <v>17508264541.341747</v>
+        <v>11734635192.615946</v>
       </c>
       <c r="T3" s="1">
-        <v>35.972162026538449</v>
+        <v>35.972162026538442</v>
       </c>
       <c r="U3" s="1">
         <v>32.080907495155614</v>
@@ -2716,25 +3532,25 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B4" t="s">
-        <v>551</v>
+        <v>823</v>
       </c>
       <c r="C4" t="s">
-        <v>606</v>
+        <v>878</v>
       </c>
       <c r="D4" t="s">
-        <v>661</v>
+        <v>933</v>
       </c>
       <c r="E4" t="s">
-        <v>716</v>
+        <v>988</v>
       </c>
       <c r="F4" s="1">
         <v>52490000</v>
       </c>
       <c r="G4" s="1">
-        <v>4209459614.8318481</v>
+        <v>2821323199.7644854</v>
       </c>
       <c r="H4" s="1">
         <v>3270000</v>
@@ -2749,7 +3565,7 @@
         <v>3.1442307692307692</v>
       </c>
       <c r="L4" s="1">
-        <v>2.821166325733186</v>
+        <v>2.8211663257331856</v>
       </c>
       <c r="M4" s="1">
         <v>3.4463497149120497</v>
@@ -2758,7 +3574,7 @@
         <v>5.4810962192438488</v>
       </c>
       <c r="O4" s="1">
-        <v>1.9428475979059405</v>
+        <v>1.942847597905941</v>
       </c>
       <c r="P4" s="1">
         <v>1.5904062769740492</v>
@@ -2770,7 +3586,7 @@
         <v>42.323394779166151</v>
       </c>
       <c r="S4" s="1">
-        <v>1271256745.4696422</v>
+        <v>852039567.31483424</v>
       </c>
       <c r="T4" s="1">
         <v>2.6119009978049714</v>
@@ -2784,25 +3600,25 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B5" t="s">
-        <v>552</v>
+        <v>824</v>
       </c>
       <c r="C5" t="s">
-        <v>607</v>
+        <v>879</v>
       </c>
       <c r="D5" t="s">
-        <v>662</v>
+        <v>934</v>
       </c>
       <c r="E5" t="s">
-        <v>717</v>
+        <v>989</v>
       </c>
       <c r="F5" s="1">
         <v>52870000</v>
       </c>
       <c r="G5" s="1">
-        <v>4239933889.0485773</v>
+        <v>2841748096.2382994</v>
       </c>
       <c r="H5" s="1">
         <v>3830000</v>
@@ -2817,7 +3633,7 @@
         <v>3.6826923076923075</v>
       </c>
       <c r="L5" s="1">
-        <v>2.8415900865215002</v>
+        <v>2.8415900865214994</v>
       </c>
       <c r="M5" s="1">
         <v>4.0365502777104432</v>
@@ -2826,7 +3642,7 @@
         <v>6.0807076669571201</v>
       </c>
       <c r="O5" s="1">
-        <v>2.1398961432895298</v>
+        <v>2.1398961432895307</v>
       </c>
       <c r="P5" s="1">
         <v>1.5064119727516774</v>
@@ -2838,10 +3654,10 @@
         <v>44.92179876773816</v>
       </c>
       <c r="S5" s="1">
-        <v>1467017065.968946</v>
+        <v>983244801.32444453</v>
       </c>
       <c r="T5" s="1">
-        <v>3.0141065933818583</v>
+        <v>3.0141065933818587</v>
       </c>
       <c r="U5" s="1">
         <v>4.2555958564447378</v>
@@ -2852,25 +3668,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B6" t="s">
-        <v>553</v>
+        <v>825</v>
       </c>
       <c r="C6" t="s">
-        <v>608</v>
+        <v>880</v>
       </c>
       <c r="D6" t="s">
-        <v>663</v>
+        <v>935</v>
       </c>
       <c r="E6" t="s">
-        <v>718</v>
+        <v>990</v>
       </c>
       <c r="F6" s="1">
         <v>174050000</v>
       </c>
       <c r="G6" s="1">
-        <v>13958019545.846508</v>
+        <v>9355140082.282505</v>
       </c>
       <c r="H6" s="1">
         <v>5890000</v>
@@ -2885,7 +3701,7 @@
         <v>5.6634615384615383</v>
       </c>
       <c r="L6" s="1">
-        <v>9.3546199084370567</v>
+        <v>9.3546199084370532</v>
       </c>
       <c r="M6" s="1">
         <v>6.2076452051473918</v>
@@ -2894,7 +3710,7 @@
         <v>4.3310356986651568</v>
       </c>
       <c r="O6" s="1">
-        <v>0.46298361035053254</v>
+        <v>0.46298361035053276</v>
       </c>
       <c r="P6" s="1">
         <v>0.69769382036748062</v>
@@ -2906,7 +3722,7 @@
         <v>57.119931110067327</v>
       </c>
       <c r="S6" s="1">
-        <v>4675936664.3333721</v>
+        <v>3133972005.6300116</v>
       </c>
       <c r="T6" s="1">
         <v>9.6070944620500622</v>
@@ -2920,25 +3736,25 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B7" t="s">
-        <v>554</v>
+        <v>826</v>
       </c>
       <c r="C7" t="s">
-        <v>609</v>
+        <v>881</v>
       </c>
       <c r="D7" t="s">
-        <v>664</v>
+        <v>936</v>
       </c>
       <c r="E7" t="s">
-        <v>719</v>
+        <v>991</v>
       </c>
       <c r="F7" s="1">
         <v>85770000</v>
       </c>
       <c r="G7" s="1">
-        <v>6878364472.5495834</v>
+        <v>4610114133.0501032</v>
       </c>
       <c r="H7" s="1">
         <v>5770000</v>
@@ -2953,7 +3769,7 @@
         <v>5.5480769230769234</v>
       </c>
       <c r="L7" s="1">
-        <v>4.6098577968781749</v>
+        <v>4.609857796878174</v>
       </c>
       <c r="M7" s="1">
         <v>6.0811736559763077</v>
@@ -2962,7 +3778,7 @@
         <v>4.9379367398903504</v>
       </c>
       <c r="O7" s="1">
-        <v>1.0711689942441072</v>
+        <v>1.0711689942441074</v>
       </c>
       <c r="P7" s="1">
         <v>0.81200390241077314</v>
@@ -2974,10 +3790,10 @@
         <v>43.937105190881624</v>
       </c>
       <c r="S7" s="1">
-        <v>1898428546.8657184</v>
+        <v>1272391468.8468595</v>
       </c>
       <c r="T7" s="1">
-        <v>3.9004767789752677</v>
+        <v>3.9004767789752681</v>
       </c>
       <c r="U7" s="1">
         <v>5.1141140215331768</v>
@@ -2988,25 +3804,25 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B8" t="s">
-        <v>555</v>
+        <v>827</v>
       </c>
       <c r="C8" t="s">
-        <v>610</v>
+        <v>882</v>
       </c>
       <c r="D8" t="s">
-        <v>665</v>
+        <v>937</v>
       </c>
       <c r="E8" t="s">
-        <v>720</v>
+        <v>992</v>
       </c>
       <c r="F8" s="1">
         <v>51025000</v>
       </c>
       <c r="G8" s="1">
-        <v>4091973268.1805115</v>
+        <v>2742579848.8851757</v>
       </c>
       <c r="H8" s="1">
         <v>2430000</v>
@@ -3021,7 +3837,7 @@
         <v>2.3365384615384612</v>
       </c>
       <c r="L8" s="1">
-        <v>2.7424273532203434</v>
+        <v>2.7424273532203429</v>
       </c>
       <c r="M8" s="1">
         <v>2.5610488707144592</v>
@@ -3030,7 +3846,7 @@
         <v>4.9289518920733304</v>
       </c>
       <c r="O8" s="1">
-        <v>1.7972953362959359</v>
+        <v>1.7972953362959361</v>
       </c>
       <c r="P8" s="1">
         <v>1.9245833019571759</v>
@@ -3042,10 +3858,10 @@
         <v>50.225279449699059</v>
       </c>
       <c r="S8" s="1">
-        <v>1194856176.7478652</v>
+        <v>800833304.10459542</v>
       </c>
       <c r="T8" s="1">
-        <v>2.4549297782709063</v>
+        <v>2.4549297782709067</v>
       </c>
       <c r="U8" s="1">
         <v>2.2786343547911927</v>
@@ -3056,25 +3872,25 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B9" t="s">
-        <v>556</v>
+        <v>828</v>
       </c>
       <c r="C9" t="s">
-        <v>611</v>
+        <v>883</v>
       </c>
       <c r="D9" t="s">
-        <v>666</v>
+        <v>938</v>
       </c>
       <c r="E9" t="s">
-        <v>721</v>
+        <v>993</v>
       </c>
       <c r="F9" s="1">
         <v>67330000</v>
       </c>
       <c r="G9" s="1">
-        <v>5399560218.4535789</v>
+        <v>3618969156.7944903</v>
       </c>
       <c r="H9" s="1">
         <v>4380000</v>
@@ -3089,7 +3905,7 @@
         <v>4.2115384615384617</v>
       </c>
       <c r="L9" s="1">
-        <v>3.6187679312557717</v>
+        <v>3.6187679312557703</v>
       </c>
       <c r="M9" s="1">
         <v>4.61621154474458</v>
@@ -3098,7 +3914,7 @@
         <v>5.1315347815325767</v>
       </c>
       <c r="O9" s="1">
-        <v>1.4180336730661394</v>
+        <v>1.41803367306614</v>
       </c>
       <c r="P9" s="1">
         <v>1.1116333668405376</v>
@@ -3110,10 +3926,10 @@
         <v>40.429468120251073</v>
       </c>
       <c r="S9" s="1">
-        <v>1533475152.2476799</v>
+        <v>1027787274.1799852</v>
       </c>
       <c r="T9" s="1">
-        <v>3.1506501692426947</v>
+        <v>3.1506501692426956</v>
       </c>
       <c r="U9" s="1">
         <v>3.9946431324636142</v>
@@ -3124,25 +3940,25 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B10" t="s">
-        <v>557</v>
+        <v>829</v>
       </c>
       <c r="C10" t="s">
-        <v>612</v>
+        <v>884</v>
       </c>
       <c r="D10" t="s">
-        <v>667</v>
+        <v>939</v>
       </c>
       <c r="E10" t="s">
-        <v>722</v>
+        <v>994</v>
       </c>
       <c r="F10" s="1">
         <v>21934000</v>
       </c>
       <c r="G10" s="1">
-        <v>1759007185.9729807</v>
+        <v>1178946524.3595774</v>
       </c>
       <c r="H10" s="1">
         <v>1380000</v>
@@ -3157,7 +3973,7 @@
         <v>1.3269230769230769</v>
       </c>
       <c r="L10" s="1">
-        <v>1.1788809713970605</v>
+        <v>1.1788809713970603</v>
       </c>
       <c r="M10" s="1">
         <v>1.4544228154674705</v>
@@ -3166,7 +3982,7 @@
         <v>2.6964714976893682</v>
       </c>
       <c r="O10" s="1">
-        <v>2.2873144644058945</v>
+        <v>2.2873144644058949</v>
       </c>
       <c r="P10" s="1">
         <v>1.8539804718497124</v>
@@ -3178,10 +3994,10 @@
         <v>45.95121337859927</v>
       </c>
       <c r="S10" s="1">
-        <v>659627694.73986781</v>
+        <v>442104946.63484156</v>
       </c>
       <c r="T10" s="1">
-        <v>1.355259069586582</v>
+        <v>1.3552590695865823</v>
       </c>
       <c r="U10" s="1">
         <v>1.6618655165667291</v>
@@ -3192,25 +4008,25 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B11" t="s">
-        <v>558</v>
+        <v>830</v>
       </c>
       <c r="C11" t="s">
-        <v>613</v>
+        <v>885</v>
       </c>
       <c r="D11" t="s">
-        <v>668</v>
+        <v>940</v>
       </c>
       <c r="E11" t="s">
-        <v>723</v>
+        <v>995</v>
       </c>
       <c r="F11" s="1">
         <v>35065000</v>
       </c>
       <c r="G11" s="1">
-        <v>2812053751.0778961</v>
+        <v>1884734196.9849815</v>
       </c>
       <c r="H11" s="1">
         <v>2520000</v>
@@ -3225,7 +4041,7 @@
         <v>2.4230769230769229</v>
       </c>
       <c r="L11" s="1">
-        <v>1.8846294001111485</v>
+        <v>1.8846294001111479</v>
       </c>
       <c r="M11" s="1">
         <v>2.6559025325927723</v>
@@ -3234,7 +4050,7 @@
         <v>4.391047701065637</v>
       </c>
       <c r="O11" s="1">
-        <v>2.3299263509349206</v>
+        <v>2.3299263509349215</v>
       </c>
       <c r="P11" s="1">
         <v>1.653316583413535</v>
@@ -3246,7 +4062,7 @@
         <v>39.645587213342601</v>
       </c>
       <c r="S11" s="1">
-        <v>1003903170.3623248</v>
+        <v>672850095.74168026</v>
       </c>
       <c r="T11" s="1">
         <v>2.0626012028752272</v>
@@ -3260,25 +4076,25 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B12" t="s">
-        <v>559</v>
+        <v>831</v>
       </c>
       <c r="C12" t="s">
-        <v>614</v>
+        <v>886</v>
       </c>
       <c r="D12" t="s">
-        <v>669</v>
+        <v>941</v>
       </c>
       <c r="E12" t="s">
-        <v>724</v>
+        <v>996</v>
       </c>
       <c r="F12" s="1">
         <v>105120000</v>
       </c>
       <c r="G12" s="1">
-        <v>8430146593.8488073</v>
+        <v>5650171361.3877449</v>
       </c>
       <c r="H12" s="1">
         <v>2860000</v>
@@ -3314,10 +4130,10 @@
         <v>29.427986132997162</v>
       </c>
       <c r="S12" s="1">
-        <v>3119154279.9221301</v>
+        <v>2090563430.6555822</v>
       </c>
       <c r="T12" s="1">
-        <v>6.408557677329398</v>
+        <v>6.4085576773293988</v>
       </c>
       <c r="U12" s="1">
         <v>3.3982340334196612</v>
@@ -3328,25 +4144,25 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B13" t="s">
-        <v>560</v>
+        <v>832</v>
       </c>
       <c r="C13" t="s">
-        <v>615</v>
+        <v>887</v>
       </c>
       <c r="D13" t="s">
-        <v>670</v>
+        <v>942</v>
       </c>
       <c r="E13" t="s">
-        <v>725</v>
+        <v>997</v>
       </c>
       <c r="F13" s="1">
         <v>46320000</v>
       </c>
       <c r="G13" s="1">
-        <v>3714653636.1023283</v>
+        <v>2489687380.7028189</v>
       </c>
       <c r="H13" s="1">
         <v>2120000</v>
@@ -3361,7 +4177,7 @@
         <v>2.0384615384615383</v>
       </c>
       <c r="L13" s="1">
-        <v>2.4895489466176643</v>
+        <v>2.4895489466176635</v>
       </c>
       <c r="M13" s="1">
         <v>2.2343307020224907</v>
@@ -3370,7 +4186,7 @@
         <v>2.6513777331737534</v>
       </c>
       <c r="O13" s="1">
-        <v>1.0650032556202407</v>
+        <v>1.0650032556202411</v>
       </c>
       <c r="P13" s="1">
         <v>1.1866541200788927</v>
@@ -3382,10 +4198,10 @@
         <v>46.930946291560105</v>
       </c>
       <c r="S13" s="1">
-        <v>1170115886.5158091</v>
+        <v>784251518.98551071</v>
       </c>
       <c r="T13" s="1">
-        <v>2.4040988277383919</v>
+        <v>2.4040988277383923</v>
       </c>
       <c r="U13" s="1">
         <v>2.1445290503640688</v>
@@ -3396,25 +4212,25 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B14" t="s">
-        <v>561</v>
+        <v>833</v>
       </c>
       <c r="C14" t="s">
-        <v>616</v>
+        <v>888</v>
       </c>
       <c r="D14" t="s">
-        <v>671</v>
+        <v>943</v>
       </c>
       <c r="E14" t="s">
-        <v>726</v>
+        <v>998</v>
       </c>
       <c r="F14" s="1">
         <v>41165000</v>
       </c>
       <c r="G14" s="1">
-        <v>3301246047.7148604</v>
+        <v>2212607535.1172614</v>
       </c>
       <c r="H14" s="1">
         <v>2380000</v>
@@ -3429,7 +4245,7 @@
         <v>2.2884615384615383</v>
       </c>
       <c r="L14" s="1">
-        <v>2.2124845075025075</v>
+        <v>2.212484507502507</v>
       </c>
       <c r="M14" s="1">
         <v>2.5083523918931738</v>
@@ -3438,7 +4254,7 @@
         <v>2.9451653042472894</v>
       </c>
       <c r="O14" s="1">
-        <v>1.3311574812208946</v>
+        <v>1.3311574812208948</v>
       </c>
       <c r="P14" s="1">
         <v>1.1741433595079644</v>
@@ -3450,10 +4266,10 @@
         <v>45.098716399009959</v>
       </c>
       <c r="S14" s="1">
-        <v>1046495002.6351595</v>
+        <v>701396592.32485902</v>
       </c>
       <c r="T14" s="1">
-        <v>2.1501096071438401</v>
+        <v>2.1501096071438406</v>
       </c>
       <c r="U14" s="1">
         <v>2.4228233125216487</v>
@@ -3464,25 +4280,25 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B15" t="s">
-        <v>562</v>
+        <v>834</v>
       </c>
       <c r="C15" t="s">
-        <v>617</v>
+        <v>889</v>
       </c>
       <c r="D15" t="s">
-        <v>672</v>
+        <v>944</v>
       </c>
       <c r="E15" t="s">
-        <v>727</v>
+        <v>999</v>
       </c>
       <c r="F15" s="1">
         <v>80260000</v>
       </c>
       <c r="G15" s="1">
-        <v>6436487496.4070139</v>
+        <v>4313953134.1797981</v>
       </c>
       <c r="H15" s="1">
         <v>2250000</v>
@@ -3497,7 +4313,7 @@
         <v>2.1634615384615383</v>
       </c>
       <c r="L15" s="1">
-        <v>4.3137132654476193</v>
+        <v>4.3137132654476185</v>
       </c>
       <c r="M15" s="1">
         <v>2.3713415469578321</v>
@@ -3506,7 +4322,7 @@
         <v>1.6540596254844189</v>
       </c>
       <c r="O15" s="1">
-        <v>0.38344218164272975</v>
+        <v>0.38344218164272981</v>
       </c>
       <c r="P15" s="1">
         <v>0.69752061975483615</v>
@@ -3518,10 +4334,10 @@
         <v>40.637491032079531</v>
       </c>
       <c r="S15" s="1">
-        <v>1930946325.6510143</v>
+        <v>1294185991.6802683</v>
       </c>
       <c r="T15" s="1">
-        <v>3.9672872160945913</v>
+        <v>3.9672872160945922</v>
       </c>
       <c r="U15" s="1">
         <v>2.1676507599173886</v>
@@ -3532,25 +4348,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B16" t="s">
-        <v>563</v>
+        <v>835</v>
       </c>
       <c r="C16" t="s">
-        <v>618</v>
+        <v>890</v>
       </c>
       <c r="D16" t="s">
-        <v>673</v>
+        <v>945</v>
       </c>
       <c r="E16" t="s">
-        <v>728</v>
+        <v>1000</v>
       </c>
       <c r="F16" s="1">
         <v>31632000</v>
       </c>
       <c r="G16" s="1">
-        <v>2536742742.1672893</v>
+        <v>1700211382.2623396</v>
       </c>
       <c r="H16" s="1">
         <v>1100000</v>
@@ -3565,7 +4381,7 @@
         <v>1.0576923076923077</v>
       </c>
       <c r="L16" s="1">
-        <v>1.7001168454104048</v>
+        <v>1.7001168454104043</v>
       </c>
       <c r="M16" s="1">
         <v>1.1593225340682736</v>
@@ -3574,7 +4390,7 @@
         <v>0.8450842710915063</v>
       </c>
       <c r="O16" s="1">
-        <v>0.49707422955832464</v>
+        <v>0.49707422955832481</v>
       </c>
       <c r="P16" s="1">
         <v>0.72894664449068536</v>
@@ -3586,10 +4402,10 @@
         <v>48.886659979939814</v>
       </c>
       <c r="S16" s="1">
-        <v>639259181.30786908</v>
+        <v>428453275.22126329</v>
       </c>
       <c r="T16" s="1">
-        <v>1.3134102921886006</v>
+        <v>1.3134102921886013</v>
       </c>
       <c r="U16" s="1">
         <v>0.89018189101759249</v>
@@ -3600,25 +4416,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B17" t="s">
-        <v>564</v>
+        <v>836</v>
       </c>
       <c r="C17" t="s">
-        <v>619</v>
+        <v>891</v>
       </c>
       <c r="D17" t="s">
-        <v>674</v>
+        <v>946</v>
       </c>
       <c r="E17" t="s">
-        <v>729</v>
+        <v>1001</v>
       </c>
       <c r="F17" s="1">
         <v>66174000</v>
       </c>
       <c r="G17" s="1">
-        <v>5306854268.4679508</v>
+        <v>3556834471.7320452</v>
       </c>
       <c r="H17" s="1">
         <v>2040000</v>
@@ -3633,7 +4449,7 @@
         <v>1.9615384615384615</v>
       </c>
       <c r="L17" s="1">
-        <v>3.5566367010681632</v>
+        <v>3.5566367010681619</v>
       </c>
       <c r="M17" s="1">
         <v>2.1500163359084343</v>
@@ -3642,7 +4458,7 @@
         <v>1.5545481977751481</v>
       </c>
       <c r="O17" s="1">
-        <v>0.43708377560976958</v>
+        <v>0.43708377560976974</v>
       </c>
       <c r="P17" s="1">
         <v>0.72304017965440881</v>
@@ -3654,7 +4470,7 @@
         <v>45.419847328244273</v>
       </c>
       <c r="S17" s="1">
-        <v>971154322.27286637</v>
+        <v>650900702.39085627</v>
       </c>
       <c r="T17" s="1">
         <v>1.9953160149644089</v>
@@ -3668,25 +4484,25 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B18" t="s">
-        <v>565</v>
+        <v>837</v>
       </c>
       <c r="C18" t="s">
-        <v>620</v>
+        <v>892</v>
       </c>
       <c r="D18" t="s">
-        <v>675</v>
+        <v>947</v>
       </c>
       <c r="E18" t="s">
-        <v>730</v>
+        <v>1002</v>
       </c>
       <c r="F18" s="1">
         <v>40361000</v>
       </c>
       <c r="G18" s="1">
-        <v>3236768899.1089392</v>
+        <v>2169392754.1568756</v>
       </c>
       <c r="H18" s="1">
         <v>808000</v>
@@ -3701,7 +4517,7 @@
         <v>0.77692307692307694</v>
       </c>
       <c r="L18" s="1">
-        <v>2.1692721294135477</v>
+        <v>2.1692721294135473</v>
       </c>
       <c r="M18" s="1">
         <v>0.85157509775196827</v>
@@ -3710,7 +4526,7 @@
         <v>1.0690273647949928</v>
       </c>
       <c r="O18" s="1">
-        <v>0.492804637232858</v>
+        <v>0.49280463723285811</v>
       </c>
       <c r="P18" s="1">
         <v>1.2553530130426152</v>
@@ -3722,10 +4538,10 @@
         <v>51.982239137329522</v>
       </c>
       <c r="S18" s="1">
-        <v>802718673.86001766</v>
+        <v>538009394.23810506</v>
       </c>
       <c r="T18" s="1">
-        <v>1.6492511938940433</v>
+        <v>1.649251193894044</v>
       </c>
       <c r="U18" s="1">
         <v>0.64350000817243436</v>
@@ -3736,25 +4552,25 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>545</v>
+        <v>817</v>
       </c>
       <c r="B19" t="s">
-        <v>566</v>
+        <v>838</v>
       </c>
       <c r="C19" t="s">
-        <v>621</v>
+        <v>893</v>
       </c>
       <c r="D19" t="s">
-        <v>676</v>
+        <v>948</v>
       </c>
       <c r="E19" t="s">
-        <v>731</v>
+        <v>1003</v>
       </c>
       <c r="F19" s="1">
         <v>17862000</v>
       </c>
       <c r="G19" s="1">
-        <v>1432451279.1031907</v>
+        <v>960077633.72439015</v>
       </c>
       <c r="H19" s="1">
         <v>855000</v>
@@ -3769,7 +4585,7 @@
         <v>0.82211538461538469</v>
       </c>
       <c r="L19" s="1">
-        <v>0.96002425052859919</v>
+        <v>0.96002425052859908</v>
       </c>
       <c r="M19" s="1">
         <v>0.90110978784397633</v>
@@ -3790,10 +4606,10 @@
         <v>46.711635750421586</v>
       </c>
       <c r="S19" s="1">
-        <v>409681084.94880044</v>
+        <v>274582216.06359494</v>
       </c>
       <c r="T19" s="1">
-        <v>0.8417233091371219</v>
+        <v>0.84172330913712212</v>
       </c>
       <c r="U19" s="1">
         <v>0.78526762074793699</v>
@@ -3804,25 +4620,25 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B20" t="s">
-        <v>567</v>
+        <v>839</v>
       </c>
       <c r="C20" t="s">
-        <v>622</v>
+        <v>894</v>
       </c>
       <c r="D20" t="s">
-        <v>677</v>
+        <v>949</v>
       </c>
       <c r="E20" t="s">
-        <v>732</v>
+        <v>1004</v>
       </c>
       <c r="F20" s="1">
         <v>301640000</v>
       </c>
       <c r="G20" s="1">
-        <v>24190158091.405575</v>
+        <v>16213067822.003418</v>
       </c>
       <c r="H20" s="1">
         <v>41300000</v>
@@ -3837,7 +4653,7 @@
         <v>17.801724137931036</v>
       </c>
       <c r="L20" s="1">
-        <v>14.320439051254297</v>
+        <v>14.320439051254294</v>
       </c>
       <c r="M20" s="1">
         <v>19.563260859267682</v>
@@ -3846,7 +4662,7 @@
         <v>34.371414522209477</v>
       </c>
       <c r="O20" s="1">
-        <v>2.4001648552248094</v>
+        <v>2.4001648552248098</v>
       </c>
       <c r="P20" s="1">
         <v>1.7569368813035453</v>
@@ -3858,10 +4674,10 @@
         <v>41.439999999999998</v>
       </c>
       <c r="S20" s="1">
-        <v>8345604512.6980076</v>
+        <v>5593508379.2636967</v>
       </c>
       <c r="T20" s="1">
-        <v>14.772782751013322</v>
+        <v>14.772782751013327</v>
       </c>
       <c r="U20" s="1">
         <v>20.170857082766823</v>
@@ -3872,25 +4688,25 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B21" t="s">
-        <v>568</v>
+        <v>840</v>
       </c>
       <c r="C21" t="s">
-        <v>623</v>
+        <v>895</v>
       </c>
       <c r="D21" t="s">
-        <v>678</v>
+        <v>950</v>
       </c>
       <c r="E21" t="s">
-        <v>733</v>
+        <v>1005</v>
       </c>
       <c r="F21" s="1">
         <v>708990000</v>
       </c>
       <c r="G21" s="1">
-        <v>56857778097.154358</v>
+        <v>38108019344.656555</v>
       </c>
       <c r="H21" s="1">
         <v>69300000</v>
@@ -3926,10 +4742,10 @@
         <v>44.770000000000003</v>
       </c>
       <c r="S21" s="1">
-        <v>19957080735.674911</v>
+        <v>13375915207.914803</v>
       </c>
       <c r="T21" s="1">
-        <v>35.326574318730472</v>
+        <v>35.326574318730479</v>
       </c>
       <c r="U21" s="1">
         <v>34.434641959795933</v>
@@ -3940,25 +4756,25 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B22" t="s">
-        <v>569</v>
+        <v>841</v>
       </c>
       <c r="C22" t="s">
-        <v>624</v>
+        <v>896</v>
       </c>
       <c r="D22" t="s">
-        <v>679</v>
+        <v>951</v>
       </c>
       <c r="E22" t="s">
-        <v>734</v>
+        <v>1006</v>
       </c>
       <c r="F22" s="1">
         <v>58590000</v>
       </c>
       <c r="G22" s="1">
-        <v>4698651911.4688129</v>
+        <v>3149196537.8967652</v>
       </c>
       <c r="H22" s="1">
         <v>7930000</v>
@@ -3973,7 +4789,7 @@
         <v>3.4181034482758625</v>
       </c>
       <c r="L22" s="1">
-        <v>2.7815757990087167</v>
+        <v>2.7815757990087162</v>
       </c>
       <c r="M22" s="1">
         <v>3.7563355596608403</v>
@@ -3982,7 +4798,7 @@
         <v>5.9662350434355025</v>
       </c>
       <c r="O22" s="1">
-        <v>2.1449119040946925</v>
+        <v>2.1449119040946929</v>
       </c>
       <c r="P22" s="1">
         <v>1.5883125851446014</v>
@@ -3994,10 +4810,10 @@
         <v>39.270000000000003</v>
       </c>
       <c r="S22" s="1">
-        <v>1353211692.2502308</v>
+        <v>906968563.87126625</v>
       </c>
       <c r="T22" s="1">
-        <v>2.3953570188148139</v>
+        <v>2.3953570188148143</v>
       </c>
       <c r="U22" s="1">
         <v>3.233112848089275</v>
@@ -4008,25 +4824,25 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B23" t="s">
-        <v>570</v>
+        <v>842</v>
       </c>
       <c r="C23" t="s">
-        <v>625</v>
+        <v>897</v>
       </c>
       <c r="D23" t="s">
-        <v>680</v>
+        <v>952</v>
       </c>
       <c r="E23" t="s">
-        <v>735</v>
+        <v>1007</v>
       </c>
       <c r="F23" s="1">
         <v>57420000</v>
       </c>
       <c r="G23" s="1">
-        <v>4604823225.0646734</v>
+        <v>3086309356.6484427</v>
       </c>
       <c r="H23" s="1">
         <v>7500000</v>
@@ -4062,10 +4878,10 @@
         <v>41.920000000000002</v>
       </c>
       <c r="S23" s="1">
-        <v>1579454342.0439239</v>
+        <v>1058604093.142079</v>
       </c>
       <c r="T23" s="1">
-        <v>2.7958353196174146</v>
+        <v>2.7958353196174159</v>
       </c>
       <c r="U23" s="1">
         <v>3.6417538148725157</v>
@@ -4076,25 +4892,25 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B24" t="s">
-        <v>571</v>
+        <v>843</v>
       </c>
       <c r="C24" t="s">
-        <v>626</v>
+        <v>898</v>
       </c>
       <c r="D24" t="s">
-        <v>681</v>
+        <v>953</v>
       </c>
       <c r="E24" t="s">
-        <v>736</v>
+        <v>1008</v>
       </c>
       <c r="F24" s="1">
         <v>203320000</v>
       </c>
       <c r="G24" s="1">
-        <v>16305340615.119287</v>
+        <v>10928394608.041821</v>
       </c>
       <c r="H24" s="1">
         <v>16100000</v>
@@ -4109,7 +4925,7 @@
         <v>6.9396551724137927</v>
       </c>
       <c r="L24" s="1">
-        <v>9.6526709584306598</v>
+        <v>9.6526709584306563</v>
       </c>
       <c r="M24" s="1">
         <v>7.6263559281890965</v>
@@ -4118,7 +4934,7 @@
         <v>4.6058023274872975</v>
       </c>
       <c r="O24" s="1">
-        <v>0.47715314728143526</v>
+        <v>0.47715314728143543</v>
       </c>
       <c r="P24" s="1">
         <v>0.60393225425828778</v>
@@ -4130,7 +4946,7 @@
         <v>58.600000000000001</v>
       </c>
       <c r="S24" s="1">
-        <v>5657953240.0963469</v>
+        <v>3792152960.2568994</v>
       </c>
       <c r="T24" s="1">
         <v>10.015297741962362</v>
@@ -4144,25 +4960,25 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B25" t="s">
-        <v>572</v>
+        <v>844</v>
       </c>
       <c r="C25" t="s">
-        <v>627</v>
+        <v>899</v>
       </c>
       <c r="D25" t="s">
-        <v>682</v>
+        <v>954</v>
       </c>
       <c r="E25" t="s">
-        <v>737</v>
+        <v>1009</v>
       </c>
       <c r="F25" s="1">
         <v>96400000</v>
       </c>
       <c r="G25" s="1">
-        <v>7730842196.0333433</v>
+        <v>5181473737.0412722</v>
       </c>
       <c r="H25" s="1">
         <v>10400000</v>
@@ -4177,7 +4993,7 @@
         <v>4.4827586206896548</v>
       </c>
       <c r="L25" s="1">
-        <v>4.5766155832811108</v>
+        <v>4.5766155832811091</v>
       </c>
       <c r="M25" s="1">
         <v>4.9263417175879871</v>
@@ -4186,7 +5002,7 @@
         <v>5.2614325520406489</v>
       </c>
       <c r="O25" s="1">
-        <v>1.1496339284560519</v>
+        <v>1.1496339284560524</v>
       </c>
       <c r="P25" s="1">
         <v>1.068020217366636</v>
@@ -4198,7 +5014,7 @@
         <v>49.439999999999998</v>
       </c>
       <c r="S25" s="1">
-        <v>2373368640.8115277</v>
+        <v>1590712495.3335721</v>
       </c>
       <c r="T25" s="1">
         <v>4.2011647287419445</v>
@@ -4212,25 +5028,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B26" t="s">
-        <v>573</v>
+        <v>845</v>
       </c>
       <c r="C26" t="s">
-        <v>628</v>
+        <v>900</v>
       </c>
       <c r="D26" t="s">
-        <v>683</v>
+        <v>955</v>
       </c>
       <c r="E26" t="s">
-        <v>738</v>
+        <v>1010</v>
       </c>
       <c r="F26" s="1">
         <v>57472000</v>
       </c>
       <c r="G26" s="1">
-        <v>4608993388.9048576</v>
+        <v>3089104342.4817014</v>
       </c>
       <c r="H26" s="1">
         <v>5090000</v>
@@ -4245,7 +5061,7 @@
         <v>2.1939655172413794</v>
       </c>
       <c r="L26" s="1">
-        <v>2.7284984523063485</v>
+        <v>2.728498452306348</v>
       </c>
       <c r="M26" s="1">
         <v>2.4110653213964284</v>
@@ -4254,7 +5070,7 @@
         <v>5.2286510408129816</v>
       </c>
       <c r="O26" s="1">
-        <v>1.9163107959226808</v>
+        <v>1.9163107959226813</v>
       </c>
       <c r="P26" s="1">
         <v>2.1686061320747121</v>
@@ -4266,10 +5082,10 @@
         <v>49.780000000000001</v>
       </c>
       <c r="S26" s="1">
-        <v>1548621757.7935088</v>
+        <v>1037939045.0803542</v>
       </c>
       <c r="T26" s="1">
-        <v>2.7412577191463323</v>
+        <v>2.7412577191463328</v>
       </c>
       <c r="U26" s="1">
         <v>2.4210973977149401</v>
@@ -4280,25 +5096,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B27" t="s">
-        <v>574</v>
+        <v>846</v>
       </c>
       <c r="C27" t="s">
-        <v>629</v>
+        <v>901</v>
       </c>
       <c r="D27" t="s">
-        <v>684</v>
+        <v>956</v>
       </c>
       <c r="E27" t="s">
-        <v>739</v>
+        <v>1011</v>
       </c>
       <c r="F27" s="1">
         <v>70690000</v>
       </c>
       <c r="G27" s="1">
-        <v>5669016958.8962345</v>
+        <v>3799568241.4050574</v>
       </c>
       <c r="H27" s="1">
         <v>8600000</v>
@@ -4313,7 +5129,7 @@
         <v>3.7068965517241379</v>
       </c>
       <c r="L27" s="1">
-        <v>3.3560265101881916</v>
+        <v>3.3560265101881912</v>
       </c>
       <c r="M27" s="1">
         <v>4.0737056510823741</v>
@@ -4322,7 +5138,7 @@
         <v>4.5566300606457961</v>
       </c>
       <c r="O27" s="1">
-        <v>1.3577455502251916</v>
+        <v>1.3577455502251918</v>
       </c>
       <c r="P27" s="1">
         <v>1.1185467117475978</v>
@@ -4334,10 +5150,10 @@
         <v>41.780000000000001</v>
       </c>
       <c r="S27" s="1">
-        <v>1502289413.011564</v>
+        <v>1006885529.6190805</v>
       </c>
       <c r="T27" s="1">
-        <v>2.6592435687313083</v>
+        <v>2.6592435687313087</v>
       </c>
       <c r="U27" s="1">
         <v>3.2262610779356597</v>
@@ -4348,25 +5164,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B28" t="s">
-        <v>575</v>
+        <v>847</v>
       </c>
       <c r="C28" t="s">
-        <v>630</v>
+        <v>902</v>
       </c>
       <c r="D28" t="s">
-        <v>685</v>
+        <v>957</v>
       </c>
       <c r="E28" t="s">
-        <v>740</v>
+        <v>1012</v>
       </c>
       <c r="F28" s="1">
         <v>24964000</v>
       </c>
       <c r="G28" s="1">
-        <v>2001999425.1221616</v>
+        <v>1341808198.874464</v>
       </c>
       <c r="H28" s="1">
         <v>3330000</v>
@@ -4381,7 +5197,7 @@
         <v>1.4353448275862069</v>
       </c>
       <c r="L28" s="1">
-        <v>1.1851725251144154</v>
+        <v>1.1851725251144152</v>
       </c>
       <c r="M28" s="1">
         <v>1.5773767230353846</v>
@@ -4390,7 +5206,7 @@
         <v>3.7534830355679403</v>
       </c>
       <c r="O28" s="1">
-        <v>3.1670351413230597</v>
+        <v>3.1670351413230606</v>
       </c>
       <c r="P28" s="1">
         <v>2.3795729839001436</v>
@@ -4402,10 +5218,10 @@
         <v>44.280000000000001</v>
       </c>
       <c r="S28" s="1">
-        <v>762761805.3145504</v>
+        <v>511228940.08668303</v>
       </c>
       <c r="T28" s="1">
-        <v>1.3501855286262254</v>
+        <v>1.3501855286262257</v>
       </c>
       <c r="U28" s="1">
         <v>1.7960748437924234</v>
@@ -4416,25 +5232,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B29" t="s">
-        <v>576</v>
+        <v>848</v>
       </c>
       <c r="C29" t="s">
-        <v>631</v>
+        <v>903</v>
       </c>
       <c r="D29" t="s">
-        <v>686</v>
+        <v>958</v>
       </c>
       <c r="E29" t="s">
-        <v>741</v>
+        <v>1013</v>
       </c>
       <c r="F29" s="1">
         <v>40140000</v>
       </c>
       <c r="G29" s="1">
-        <v>3219045702.7881575</v>
+        <v>2157514064.3655257</v>
       </c>
       <c r="H29" s="1">
         <v>5320000</v>
@@ -4449,7 +5265,7 @@
         <v>2.2931034482758621</v>
       </c>
       <c r="L29" s="1">
-        <v>1.9056571526234831</v>
+        <v>1.9056571526234829</v>
       </c>
       <c r="M29" s="1">
         <v>2.520013263227701</v>
@@ -4458,7 +5274,7 @@
         <v>4.5894115718734634</v>
       </c>
       <c r="O29" s="1">
-        <v>2.4083091575813125</v>
+        <v>2.4083091575813129</v>
       </c>
       <c r="P29" s="1">
         <v>1.8211854829665544</v>
@@ -4470,10 +5286,10 @@
         <v>40.119999999999997</v>
       </c>
       <c r="S29" s="1">
-        <v>1055847019.6787671</v>
+        <v>707664632.6587671</v>
       </c>
       <c r="T29" s="1">
-        <v>1.8689836807252183</v>
+        <v>1.8689836807252189</v>
       </c>
       <c r="U29" s="1">
         <v>2.4702487889232354</v>
@@ -4484,25 +5300,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B30" t="s">
-        <v>577</v>
+        <v>849</v>
       </c>
       <c r="C30" t="s">
-        <v>632</v>
+        <v>904</v>
       </c>
       <c r="D30" t="s">
-        <v>687</v>
+        <v>959</v>
       </c>
       <c r="E30" t="s">
-        <v>742</v>
+        <v>1014</v>
       </c>
       <c r="F30" s="1">
         <v>118270000</v>
       </c>
       <c r="G30" s="1">
-        <v>9484716872.6645584</v>
+        <v>6356980278.8368397</v>
       </c>
       <c r="H30" s="1">
         <v>8210000</v>
@@ -4517,7 +5333,7 @@
         <v>3.5387931034482762</v>
       </c>
       <c r="L30" s="1">
-        <v>5.614899637288973</v>
+        <v>5.6148996372889721</v>
       </c>
       <c r="M30" s="1">
         <v>3.8889678366728249</v>
@@ -4526,7 +5342,7 @@
         <v>2.6553024094410755</v>
       </c>
       <c r="O30" s="1">
-        <v>0.47290291562951747</v>
+        <v>0.47290291562951758</v>
       </c>
       <c r="P30" s="1">
         <v>0.68277818715847194</v>
@@ -4538,10 +5354,10 @@
         <v>31.98</v>
       </c>
       <c r="S30" s="1">
-        <v>4021519906.5217857</v>
+        <v>2695359606.3987536</v>
       </c>
       <c r="T30" s="1">
-        <v>7.1186023513970351</v>
+        <v>7.1186023513970369</v>
       </c>
       <c r="U30" s="1">
         <v>4.9279264310541615</v>
@@ -4552,25 +5368,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B31" t="s">
-        <v>578</v>
+        <v>850</v>
       </c>
       <c r="C31" t="s">
-        <v>633</v>
+        <v>905</v>
       </c>
       <c r="D31" t="s">
-        <v>688</v>
+        <v>960</v>
       </c>
       <c r="E31" t="s">
-        <v>743</v>
+        <v>1015</v>
       </c>
       <c r="F31" s="1">
         <v>50900000</v>
       </c>
       <c r="G31" s="1">
-        <v>4081948835.8723769</v>
+        <v>2735861132.9398422</v>
       </c>
       <c r="H31" s="1">
         <v>5040000</v>
@@ -4606,10 +5422,10 @@
         <v>47.009999999999998</v>
       </c>
       <c r="S31" s="1">
-        <v>1196011060.4908659</v>
+        <v>801607346.52222037</v>
       </c>
       <c r="T31" s="1">
-        <v>2.1170918820269722</v>
+        <v>2.1170918820269726</v>
       </c>
       <c r="U31" s="1">
         <v>2.0905154548756264</v>
@@ -4620,25 +5436,25 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B32" t="s">
-        <v>579</v>
+        <v>851</v>
       </c>
       <c r="C32" t="s">
-        <v>634</v>
+        <v>906</v>
       </c>
       <c r="D32" t="s">
-        <v>689</v>
+        <v>961</v>
       </c>
       <c r="E32" t="s">
-        <v>744</v>
+        <v>1016</v>
       </c>
       <c r="F32" s="1">
         <v>44168000</v>
       </c>
       <c r="G32" s="1">
-        <v>3542073009.4854841</v>
+        <v>2374017966.9879556</v>
       </c>
       <c r="H32" s="1">
         <v>4770000</v>
@@ -4653,7 +5469,7 @@
         <v>2.0560344827586206</v>
       </c>
       <c r="L32" s="1">
-        <v>2.0968875216012459</v>
+        <v>2.096887521601245</v>
       </c>
       <c r="M32" s="1">
         <v>2.2594855762398747</v>
@@ -4662,7 +5478,7 @@
         <v>2.1471889854122277</v>
       </c>
       <c r="O32" s="1">
-        <v>1.0239886323385481</v>
+        <v>1.0239886323385485</v>
       </c>
       <c r="P32" s="1">
         <v>0.95029993021043069</v>
@@ -4674,10 +5490,10 @@
         <v>46.509999999999998</v>
       </c>
       <c r="S32" s="1">
-        <v>1044911491.350937</v>
+        <v>700335269.1308974</v>
       </c>
       <c r="T32" s="1">
-        <v>1.8496264030098908</v>
+        <v>1.8496264030098912</v>
       </c>
       <c r="U32" s="1">
         <v>1.9920286612921014</v>
@@ -4688,25 +5504,25 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B33" t="s">
-        <v>580</v>
+        <v>852</v>
       </c>
       <c r="C33" t="s">
-        <v>635</v>
+        <v>907</v>
       </c>
       <c r="D33" t="s">
-        <v>690</v>
+        <v>962</v>
       </c>
       <c r="E33" t="s">
-        <v>745</v>
+        <v>1017</v>
       </c>
       <c r="F33" s="1">
         <v>88840000</v>
       </c>
       <c r="G33" s="1">
-        <v>7124564530.0373669</v>
+        <v>4775125796.6674967</v>
       </c>
       <c r="H33" s="1">
         <v>5380000</v>
@@ -4742,10 +5558,10 @@
         <v>46.159999999999997</v>
       </c>
       <c r="S33" s="1">
-        <v>2087497497.3282619</v>
+        <v>1399111918.762948</v>
       </c>
       <c r="T33" s="1">
-        <v>3.6951364007716343</v>
+        <v>3.6951364007716356</v>
       </c>
       <c r="U33" s="1">
         <v>2.2315422911172367</v>
@@ -4756,25 +5572,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B34" t="s">
-        <v>581</v>
+        <v>853</v>
       </c>
       <c r="C34" t="s">
-        <v>636</v>
+        <v>908</v>
       </c>
       <c r="D34" t="s">
-        <v>691</v>
+        <v>963</v>
       </c>
       <c r="E34" t="s">
-        <v>746</v>
+        <v>1018</v>
       </c>
       <c r="F34" s="1">
         <v>37369000</v>
       </c>
       <c r="G34" s="1">
-        <v>2996824087.3814316</v>
+        <v>2008573569.2893705</v>
       </c>
       <c r="H34" s="1">
         <v>3020000</v>
@@ -4789,7 +5605,7 @@
         <v>1.3017241379310345</v>
       </c>
       <c r="L34" s="1">
-        <v>1.7741031922368447</v>
+        <v>1.7741031922368442</v>
       </c>
       <c r="M34" s="1">
         <v>1.4305338449149732</v>
@@ -4798,7 +5614,7 @@
         <v>1.4751680052450418</v>
       </c>
       <c r="O34" s="1">
-        <v>0.83150067690544194</v>
+        <v>0.83150067690544216</v>
       </c>
       <c r="P34" s="1">
         <v>1.0312010516135126</v>
@@ -4810,10 +5626,10 @@
         <v>47.899999999999999</v>
       </c>
       <c r="S34" s="1">
-        <v>875072620.65440428</v>
+        <v>586503473.61263359</v>
       </c>
       <c r="T34" s="1">
-        <v>1.5489899738980346</v>
+        <v>1.5489899738980351</v>
       </c>
       <c r="U34" s="1">
         <v>1.2483748050605898</v>
@@ -4824,25 +5640,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B35" t="s">
-        <v>582</v>
+        <v>854</v>
       </c>
       <c r="C35" t="s">
-        <v>637</v>
+        <v>909</v>
       </c>
       <c r="D35" t="s">
-        <v>692</v>
+        <v>964</v>
       </c>
       <c r="E35" t="s">
-        <v>747</v>
+        <v>1019</v>
       </c>
       <c r="F35" s="1">
         <v>73577000</v>
       </c>
       <c r="G35" s="1">
-        <v>5900541247.4849091</v>
+        <v>3954743704.8784823</v>
       </c>
       <c r="H35" s="1">
         <v>5130000</v>
@@ -4857,7 +5673,7 @@
         <v>2.2112068965517242</v>
       </c>
       <c r="L35" s="1">
-        <v>3.4930876013596914</v>
+        <v>3.493087601359691</v>
       </c>
       <c r="M35" s="1">
         <v>2.4300127895409975</v>
@@ -4866,7 +5682,7 @@
         <v>1.4587772496312081</v>
       </c>
       <c r="O35" s="1">
-        <v>0.41761828391116679</v>
+        <v>0.41761828391116684</v>
       </c>
       <c r="P35" s="1">
         <v>0.60031669623712347</v>
@@ -4878,10 +5694,10 @@
         <v>44.039999999999999</v>
       </c>
       <c r="S35" s="1">
-        <v>1174207713.8766916</v>
+        <v>786994001.04235554</v>
       </c>
       <c r="T35" s="1">
-        <v>2.0784971819922213</v>
+        <v>2.0784971819922218</v>
       </c>
       <c r="U35" s="1">
         <v>1.4451923388369883</v>
@@ -4892,25 +5708,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B36" t="s">
-        <v>583</v>
+        <v>855</v>
       </c>
       <c r="C36" t="s">
-        <v>638</v>
+        <v>910</v>
       </c>
       <c r="D36" t="s">
-        <v>693</v>
+        <v>965</v>
       </c>
       <c r="E36" t="s">
-        <v>748</v>
+        <v>1020</v>
       </c>
       <c r="F36" s="1">
         <v>53393000</v>
       </c>
       <c r="G36" s="1">
-        <v>4281876113.8258119</v>
+        <v>2869859203.7535753</v>
       </c>
       <c r="H36" s="1">
         <v>2790000</v>
@@ -4925,7 +5741,7 @@
         <v>1.2025862068965518</v>
       </c>
       <c r="L36" s="1">
-        <v>2.5348468447938628</v>
+        <v>2.5348468447938619</v>
       </c>
       <c r="M36" s="1">
         <v>1.3215859030837005</v>
@@ -4934,7 +5750,7 @@
         <v>1.0817898705130307</v>
       </c>
       <c r="O36" s="1">
-        <v>0.42676734996232218</v>
+        <v>0.42676734996232235</v>
       </c>
       <c r="P36" s="1">
         <v>0.81855433535485989</v>
@@ -4946,10 +5762,10 @@
         <v>54.799999999999997</v>
       </c>
       <c r="S36" s="1">
-        <v>1365918504.8115256</v>
+        <v>915485102.41885662</v>
       </c>
       <c r="T36" s="1">
-        <v>2.4178496951859794</v>
+        <v>2.4178496951859803</v>
       </c>
       <c r="U36" s="1">
         <v>1.2599406882326083</v>
@@ -4960,25 +5776,25 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>546</v>
+        <v>818</v>
       </c>
       <c r="B37" t="s">
-        <v>584</v>
+        <v>856</v>
       </c>
       <c r="C37" t="s">
-        <v>639</v>
+        <v>911</v>
       </c>
       <c r="D37" t="s">
-        <v>694</v>
+        <v>966</v>
       </c>
       <c r="E37" t="s">
-        <v>749</v>
+        <v>1021</v>
       </c>
       <c r="F37" s="1">
         <v>20217000</v>
       </c>
       <c r="G37" s="1">
-        <v>1621311583.788445</v>
+        <v>1086658242.1344752</v>
       </c>
       <c r="H37" s="1">
         <v>1900000</v>
@@ -4993,7 +5809,7 @@
         <v>0.81896551724137934</v>
       </c>
       <c r="L37" s="1">
-        <v>0.95980744032359144</v>
+        <v>0.95980744032359133</v>
       </c>
       <c r="M37" s="1">
         <v>0.90000473686703619</v>
@@ -5014,10 +5830,10 @@
         <v>49.799999999999997</v>
       </c>
       <c r="S37" s="1">
-        <v>591778743.54481459</v>
+        <v>396630268.74226403</v>
       </c>
       <c r="T37" s="1">
-        <v>1.0475237356088116</v>
+        <v>1.0475237356088118</v>
       </c>
       <c r="U37" s="1">
         <v>0.98175174935789322</v>
@@ -5028,25 +5844,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B38" t="s">
-        <v>585</v>
+        <v>857</v>
       </c>
       <c r="C38" t="s">
-        <v>640</v>
+        <v>912</v>
       </c>
       <c r="D38" t="s">
-        <v>695</v>
+        <v>967</v>
       </c>
       <c r="E38" t="s">
-        <v>750</v>
+        <v>1022</v>
       </c>
       <c r="F38" s="1">
         <v>293620000</v>
       </c>
       <c r="G38" s="1">
-        <v>23546990514.515667</v>
+        <v>15781995006.950813</v>
       </c>
       <c r="H38" s="1">
         <v>40900000</v>
@@ -5061,7 +5877,7 @@
         <v>16.693877551020407</v>
       </c>
       <c r="L38" s="1">
-        <v>13.632339128694722</v>
+        <v>13.632339128694726</v>
       </c>
       <c r="M38" s="1">
         <v>18.413470196290294</v>
@@ -5070,7 +5886,7 @@
         <v>31.833254381809567</v>
       </c>
       <c r="O38" s="1">
-        <v>2.3351278222534622</v>
+        <v>2.3351278222534617</v>
       </c>
       <c r="P38" s="1">
         <v>1.7288025582610125</v>
@@ -5082,10 +5898,10 @@
         <v>41.32</v>
       </c>
       <c r="S38" s="1">
-        <v>7558584185.3351698</v>
+        <v>5066020551.5027647</v>
       </c>
       <c r="T38" s="1">
-        <v>13.634812330348028</v>
+        <v>13.634812330348019</v>
       </c>
       <c r="U38" s="1">
         <v>18.44450549590611</v>
@@ -5096,25 +5912,25 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B39" t="s">
-        <v>586</v>
+        <v>858</v>
       </c>
       <c r="C39" t="s">
-        <v>641</v>
+        <v>913</v>
       </c>
       <c r="D39" t="s">
-        <v>696</v>
+        <v>968</v>
       </c>
       <c r="E39" t="s">
-        <v>751</v>
+        <v>1023</v>
       </c>
       <c r="F39" s="1">
         <v>724030000</v>
       </c>
       <c r="G39" s="1">
-        <v>58063917792.469101</v>
+        <v>38916415247.199097</v>
       </c>
       <c r="H39" s="1">
         <v>72300000</v>
@@ -5129,7 +5945,7 @@
         <v>29.510204081632651</v>
       </c>
       <c r="L39" s="1">
-        <v>33.615634150769154</v>
+        <v>33.615634150769168</v>
       </c>
       <c r="M39" s="1">
         <v>32.549972987574286</v>
@@ -5138,7 +5954,7 @@
         <v>11.242696984051792</v>
       </c>
       <c r="O39" s="1">
-        <v>0.33444845733468187</v>
+        <v>0.3344484573346817</v>
       </c>
       <c r="P39" s="1">
         <v>0.34539804344364922</v>
@@ -5150,10 +5966,10 @@
         <v>44.140000000000001</v>
       </c>
       <c r="S39" s="1">
-        <v>19277219973.393353</v>
+        <v>12920249370.31509</v>
       </c>
       <c r="T39" s="1">
-        <v>34.773876977914462</v>
+        <v>34.773876977914448</v>
       </c>
       <c r="U39" s="1">
         <v>33.722132226496917</v>
@@ -5164,25 +5980,25 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B40" t="s">
-        <v>587</v>
+        <v>859</v>
       </c>
       <c r="C40" t="s">
-        <v>642</v>
+        <v>914</v>
       </c>
       <c r="D40" t="s">
-        <v>697</v>
+        <v>969</v>
       </c>
       <c r="E40" t="s">
-        <v>752</v>
+        <v>1024</v>
       </c>
       <c r="F40" s="1">
         <v>59780000</v>
       </c>
       <c r="G40" s="1">
-        <v>4794084507.0422535</v>
+        <v>3213158713.696341</v>
       </c>
       <c r="H40" s="1">
         <v>8340000</v>
@@ -5197,7 +6013,7 @@
         <v>3.4040816326530612</v>
       </c>
       <c r="L40" s="1">
-        <v>2.7754963323798463</v>
+        <v>2.7754963323798472</v>
       </c>
       <c r="M40" s="1">
         <v>3.7547271745002697</v>
@@ -5206,7 +6022,7 @@
         <v>6.2371703773882832</v>
       </c>
       <c r="O40" s="1">
-        <v>2.2472270291347236</v>
+        <v>2.2472270291347227</v>
       </c>
       <c r="P40" s="1">
         <v>1.6611514199346351</v>
@@ -5218,10 +6034,10 @@
         <v>34.229999999999997</v>
       </c>
       <c r="S40" s="1">
-        <v>1222491526.4357984</v>
+        <v>819355456.67103231</v>
       </c>
       <c r="T40" s="1">
-        <v>2.2052334312465791</v>
+        <v>2.2052334312465782</v>
       </c>
       <c r="U40" s="1">
         <v>2.9877543366254535</v>
@@ -5232,25 +6048,25 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B41" t="s">
-        <v>588</v>
+        <v>860</v>
       </c>
       <c r="C41" t="s">
-        <v>643</v>
+        <v>915</v>
       </c>
       <c r="D41" t="s">
-        <v>698</v>
+        <v>970</v>
       </c>
       <c r="E41" t="s">
-        <v>753</v>
+        <v>1025</v>
       </c>
       <c r="F41" s="1">
         <v>56300000</v>
       </c>
       <c r="G41" s="1">
-        <v>4515004311.5837889</v>
+        <v>3026109661.7782536</v>
       </c>
       <c r="H41" s="1">
         <v>7310000</v>
@@ -5265,7 +6081,7 @@
         <v>2.9836734693877549</v>
       </c>
       <c r="L41" s="1">
-        <v>2.6139251173132378</v>
+        <v>2.6139251173132383</v>
       </c>
       <c r="M41" s="1">
         <v>3.2910138663785347</v>
@@ -5286,10 +6102,10 @@
         <v>39.020000000000003</v>
       </c>
       <c r="S41" s="1">
-        <v>1471891428.1819944</v>
+        <v>986511764.89080679</v>
       </c>
       <c r="T41" s="1">
-        <v>2.6551220310341108</v>
+        <v>2.6551220310341095</v>
       </c>
       <c r="U41" s="1">
         <v>3.3479090101705711</v>
@@ -5300,25 +6116,25 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B42" t="s">
-        <v>589</v>
+        <v>861</v>
       </c>
       <c r="C42" t="s">
-        <v>644</v>
+        <v>916</v>
       </c>
       <c r="D42" t="s">
-        <v>699</v>
+        <v>971</v>
       </c>
       <c r="E42" t="s">
-        <v>754</v>
+        <v>1026</v>
       </c>
       <c r="F42" s="1">
         <v>209550000</v>
       </c>
       <c r="G42" s="1">
-        <v>16804958321.356712</v>
+        <v>11263255410.757248</v>
       </c>
       <c r="H42" s="1">
         <v>17900000</v>
@@ -5333,7 +6149,7 @@
         <v>7.3061224489795924</v>
       </c>
       <c r="L42" s="1">
-        <v>9.7290942865539769</v>
+        <v>9.7290942865539805</v>
       </c>
       <c r="M42" s="1">
         <v>8.0587070052224021</v>
@@ -5342,7 +6158,7 @@
         <v>5.2581714827096153</v>
       </c>
       <c r="O42" s="1">
-        <v>0.54045847720651985</v>
+        <v>0.54045847720651963</v>
       </c>
       <c r="P42" s="1">
         <v>0.65248326801087142</v>
@@ -5354,10 +6170,10 @@
         <v>57.350000000000001</v>
       </c>
       <c r="S42" s="1">
-        <v>5948955281.8198051</v>
+        <v>3987192439.5763898</v>
       </c>
       <c r="T42" s="1">
-        <v>10.731227812030902</v>
+        <v>10.731227812030895</v>
       </c>
       <c r="U42" s="1">
         <v>8.9021510312883301</v>
@@ -5368,25 +6184,25 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B43" t="s">
-        <v>590</v>
+        <v>862</v>
       </c>
       <c r="C43" t="s">
-        <v>645</v>
+        <v>917</v>
       </c>
       <c r="D43" t="s">
-        <v>700</v>
+        <v>972</v>
       </c>
       <c r="E43" t="s">
-        <v>755</v>
+        <v>1027</v>
       </c>
       <c r="F43" s="1">
         <v>101730000</v>
       </c>
       <c r="G43" s="1">
-        <v>8158283989.6521988</v>
+        <v>5467959784.9502974</v>
       </c>
       <c r="H43" s="1">
         <v>10600000</v>
@@ -5401,7 +6217,7 @@
         <v>4.3265306122448974</v>
       </c>
       <c r="L43" s="1">
-        <v>4.7231723300937061</v>
+        <v>4.7231723300937078</v>
       </c>
       <c r="M43" s="1">
         <v>4.7721952097965064</v>
@@ -5410,7 +6226,7 @@
         <v>5.1792199589452066</v>
       </c>
       <c r="O43" s="1">
-        <v>1.0965553651188613</v>
+        <v>1.0965553651188609</v>
       </c>
       <c r="P43" s="1">
         <v>1.0852908842272728</v>
@@ -5422,10 +6238,10 @@
         <v>47</v>
       </c>
       <c r="S43" s="1">
-        <v>2268002925.7822738</v>
+        <v>1520092804.5722241</v>
       </c>
       <c r="T43" s="1">
-        <v>4.0912151666867089</v>
+        <v>4.0912151666867071</v>
       </c>
       <c r="U43" s="1">
         <v>4.1398949326162491</v>
@@ -5436,25 +6252,25 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B44" t="s">
-        <v>591</v>
+        <v>863</v>
       </c>
       <c r="C44" t="s">
-        <v>646</v>
+        <v>918</v>
       </c>
       <c r="D44" t="s">
-        <v>701</v>
+        <v>973</v>
       </c>
       <c r="E44" t="s">
-        <v>756</v>
+        <v>1028</v>
       </c>
       <c r="F44" s="1">
         <v>60970000</v>
       </c>
       <c r="G44" s="1">
-        <v>4889517102.615694</v>
+        <v>3277120889.4959168</v>
       </c>
       <c r="H44" s="1">
         <v>5830000</v>
@@ -5469,7 +6285,7 @@
         <v>2.379591836734694</v>
       </c>
       <c r="L44" s="1">
-        <v>2.830746259371014</v>
+        <v>2.8307462593710149</v>
       </c>
       <c r="M44" s="1">
         <v>2.6247073653880784</v>
@@ -5478,7 +6294,7 @@
         <v>5.1160587399336803</v>
       </c>
       <c r="O44" s="1">
-        <v>1.8073180254137149</v>
+        <v>1.8073180254137142</v>
       </c>
       <c r="P44" s="1">
         <v>1.949192053711954</v>
@@ -5490,10 +6306,10 @@
         <v>47.240000000000002</v>
       </c>
       <c r="S44" s="1">
-        <v>1549976929.6894372</v>
+        <v>1038847327.4394912</v>
       </c>
       <c r="T44" s="1">
-        <v>2.7959792514697499</v>
+        <v>2.7959792514697481</v>
       </c>
       <c r="U44" s="1">
         <v>2.5963693983092546</v>
@@ -5504,25 +6320,25 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B45" t="s">
-        <v>592</v>
+        <v>864</v>
       </c>
       <c r="C45" t="s">
-        <v>647</v>
+        <v>919</v>
       </c>
       <c r="D45" t="s">
-        <v>702</v>
+        <v>974</v>
       </c>
       <c r="E45" t="s">
-        <v>757</v>
+        <v>1029</v>
       </c>
       <c r="F45" s="1">
         <v>69110000</v>
       </c>
       <c r="G45" s="1">
-        <v>5542308134.5214138</v>
+        <v>3714643671.856041</v>
       </c>
       <c r="H45" s="1">
         <v>8580000</v>
@@ -5537,7 +6353,7 @@
         <v>3.5020408163265309</v>
       </c>
       <c r="L45" s="1">
-        <v>3.2086743313946329</v>
+        <v>3.2086743313946342</v>
       </c>
       <c r="M45" s="1">
         <v>3.8627768773635869</v>
@@ -5546,7 +6362,7 @@
         <v>4.7055108163587551</v>
       </c>
       <c r="O45" s="1">
-        <v>1.4664968552023572</v>
+        <v>1.4664968552023565</v>
       </c>
       <c r="P45" s="1">
         <v>1.2181679050461618</v>
@@ -5558,10 +6374,10 @@
         <v>37.619999999999997</v>
       </c>
       <c r="S45" s="1">
-        <v>1446542464.0731552</v>
+        <v>969522025.80926871</v>
       </c>
       <c r="T45" s="1">
-        <v>2.6093954293428414</v>
+        <v>2.6093954293428401</v>
       </c>
       <c r="U45" s="1">
         <v>3.146056153163364</v>
@@ -5572,25 +6388,25 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B46" t="s">
-        <v>593</v>
+        <v>865</v>
       </c>
       <c r="C46" t="s">
-        <v>648</v>
+        <v>920</v>
       </c>
       <c r="D46" t="s">
-        <v>703</v>
+        <v>975</v>
       </c>
       <c r="E46" t="s">
-        <v>758</v>
+        <v>1030</v>
       </c>
       <c r="F46" s="1">
         <v>26118000</v>
       </c>
       <c r="G46" s="1">
-        <v>2094544984.1908596</v>
+        <v>1403835384.4817839</v>
       </c>
       <c r="H46" s="1">
         <v>3900000</v>
@@ -5605,7 +6421,7 @@
         <v>1.5918367346938775</v>
       </c>
       <c r="L46" s="1">
-        <v>1.2126198261809438</v>
+        <v>1.2126198261809444</v>
       </c>
       <c r="M46" s="1">
         <v>1.7558076715289033</v>
@@ -5614,7 +6430,7 @@
         <v>4.1844307595136581</v>
       </c>
       <c r="O46" s="1">
-        <v>3.4507358936165611</v>
+        <v>3.4507358936165593</v>
       </c>
       <c r="P46" s="1">
         <v>2.383194257187625</v>
@@ -5626,10 +6442,10 @@
         <v>42.670000000000002</v>
       </c>
       <c r="S46" s="1">
-        <v>831534389.68523443</v>
+        <v>557322668.39069533</v>
       </c>
       <c r="T46" s="1">
-        <v>1.4999919391763583</v>
+        <v>1.4999919391763579</v>
       </c>
       <c r="U46" s="1">
         <v>2.1751729431244762</v>
@@ -5640,25 +6456,25 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B47" t="s">
-        <v>594</v>
+        <v>866</v>
       </c>
       <c r="C47" t="s">
-        <v>649</v>
+        <v>921</v>
       </c>
       <c r="D47" t="s">
-        <v>704</v>
+        <v>976</v>
       </c>
       <c r="E47" t="s">
-        <v>759</v>
+        <v>1031</v>
       </c>
       <c r="F47" s="1">
         <v>39835000</v>
       </c>
       <c r="G47" s="1">
-        <v>3194586087.9563093</v>
+        <v>2141120397.4589117</v>
       </c>
       <c r="H47" s="1">
         <v>5330000</v>
@@ -5673,7 +6489,7 @@
         <v>2.175510204081633</v>
       </c>
       <c r="L47" s="1">
-        <v>1.8494796989018263</v>
+        <v>1.8494796989018267</v>
       </c>
       <c r="M47" s="1">
         <v>2.3996038177561676</v>
@@ -5682,7 +6498,7 @@
         <v>4.1528501500078949</v>
       </c>
       <c r="O47" s="1">
-        <v>2.2454153741042688</v>
+        <v>2.2454153741042684</v>
       </c>
       <c r="P47" s="1">
         <v>1.7306399161721457</v>
@@ -5694,10 +6510,10 @@
         <v>42.109999999999999</v>
       </c>
       <c r="S47" s="1">
-        <v>1051018810.7512469</v>
+        <v>704428602.59625578</v>
       </c>
       <c r="T47" s="1">
-        <v>1.8959164691268657</v>
+        <v>1.8959164691268646</v>
       </c>
       <c r="U47" s="1">
         <v>2.4635521744013507</v>
@@ -5708,25 +6524,25 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B48" t="s">
-        <v>595</v>
+        <v>867</v>
       </c>
       <c r="C48" t="s">
-        <v>650</v>
+        <v>922</v>
       </c>
       <c r="D48" t="s">
-        <v>705</v>
+        <v>977</v>
       </c>
       <c r="E48" t="s">
-        <v>760</v>
+        <v>1032</v>
       </c>
       <c r="F48" s="1">
         <v>126909000</v>
       </c>
       <c r="G48" s="1">
-        <v>10177525438.344353</v>
+        <v>6821324175.2507353</v>
       </c>
       <c r="H48" s="1">
         <v>9900000</v>
@@ -5741,7 +6557,7 @@
         <v>4.0408163265306118</v>
       </c>
       <c r="L48" s="1">
-        <v>5.8921957853127118</v>
+        <v>5.8921957853127136</v>
       </c>
       <c r="M48" s="1">
         <v>4.4570502431118308</v>
@@ -5750,7 +6566,7 @@
         <v>3.2843833885993998</v>
       </c>
       <c r="O48" s="1">
-        <v>0.55741246697644997</v>
+        <v>0.55741246697644986</v>
       </c>
       <c r="P48" s="1">
         <v>0.73689620027848357</v>
@@ -5762,10 +6578,10 @@
         <v>29.41</v>
       </c>
       <c r="S48" s="1">
-        <v>4152430301.1961389</v>
+        <v>2783100211.4597268</v>
       </c>
       <c r="T48" s="1">
-        <v>7.4905043700521148</v>
+        <v>7.4905043700521121</v>
       </c>
       <c r="U48" s="1">
         <v>5.6745837760368323</v>
@@ -5776,25 +6592,25 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B49" t="s">
-        <v>596</v>
+        <v>868</v>
       </c>
       <c r="C49" t="s">
-        <v>651</v>
+        <v>923</v>
       </c>
       <c r="D49" t="s">
-        <v>706</v>
+        <v>978</v>
       </c>
       <c r="E49" t="s">
-        <v>761</v>
+        <v>1033</v>
       </c>
       <c r="F49" s="1">
         <v>53340000</v>
       </c>
       <c r="G49" s="1">
-        <v>4277625754.527163</v>
+        <v>2867010468.1927538</v>
       </c>
       <c r="H49" s="1">
         <v>5680000</v>
@@ -5809,7 +6625,7 @@
         <v>2.3183673469387758</v>
       </c>
       <c r="L49" s="1">
-        <v>2.4764967274864667</v>
+        <v>2.4764967274864675</v>
       </c>
       <c r="M49" s="1">
         <v>2.5571763010985054</v>
@@ -5818,7 +6634,7 @@
         <v>3.2370124743407542</v>
       </c>
       <c r="O49" s="1">
-        <v>1.3070933784863819</v>
+        <v>1.3070933784863814</v>
       </c>
       <c r="P49" s="1">
         <v>1.2658542443671978</v>
@@ -5830,10 +6646,10 @@
         <v>42.280000000000001</v>
       </c>
       <c r="S49" s="1">
-        <v>1274732508.5046546</v>
+        <v>854369142.07854319</v>
       </c>
       <c r="T49" s="1">
-        <v>2.2994701254470482</v>
+        <v>2.2994701254470473</v>
       </c>
       <c r="U49" s="1">
         <v>2.3779530391841592</v>
@@ -5844,25 +6660,25 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B50" t="s">
-        <v>597</v>
+        <v>869</v>
       </c>
       <c r="C50" t="s">
-        <v>652</v>
+        <v>924</v>
       </c>
       <c r="D50" t="s">
-        <v>707</v>
+        <v>979</v>
       </c>
       <c r="E50" t="s">
-        <v>762</v>
+        <v>1034</v>
       </c>
       <c r="F50" s="1">
         <v>47617000</v>
       </c>
       <c r="G50" s="1">
-        <v>3818667145.7315321</v>
+        <v>2559400777.3516002</v>
       </c>
       <c r="H50" s="1">
         <v>5580000</v>
@@ -5877,7 +6693,7 @@
         <v>2.277551020408163</v>
       </c>
       <c r="L50" s="1">
-        <v>2.2107863643180186</v>
+        <v>2.210786364318019</v>
       </c>
       <c r="M50" s="1">
         <v>2.5121555915721232</v>
@@ -5886,7 +6702,7 @@
         <v>2.3685457129322596</v>
       </c>
       <c r="O50" s="1">
-        <v>1.0713589296371957</v>
+        <v>1.0713589296371955</v>
       </c>
       <c r="P50" s="1">
         <v>0.94283400314787369</v>
@@ -5898,10 +6714,10 @@
         <v>42.890000000000001</v>
       </c>
       <c r="S50" s="1">
-        <v>1164693506.7613533</v>
+        <v>780617255.39849901</v>
       </c>
       <c r="T50" s="1">
-        <v>2.1009724834283632</v>
+        <v>2.1009724834283623</v>
       </c>
       <c r="U50" s="1">
         <v>2.3909622042752798</v>
@@ -5912,25 +6728,25 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B51" t="s">
-        <v>598</v>
+        <v>870</v>
       </c>
       <c r="C51" t="s">
-        <v>653</v>
+        <v>925</v>
       </c>
       <c r="D51" t="s">
-        <v>708</v>
+        <v>980</v>
       </c>
       <c r="E51" t="s">
-        <v>763</v>
+        <v>1035</v>
       </c>
       <c r="F51" s="1">
         <v>92580000</v>
       </c>
       <c r="G51" s="1">
-        <v>7424495544.6967516</v>
+        <v>4976149777.7518778</v>
       </c>
       <c r="H51" s="1">
         <v>5860000</v>
@@ -5945,7 +6761,7 @@
         <v>2.3918367346938774</v>
       </c>
       <c r="L51" s="1">
-        <v>4.2983514628927093</v>
+        <v>4.2983514628927102</v>
       </c>
       <c r="M51" s="1">
         <v>2.6382135782459932</v>
@@ -5954,7 +6770,7 @@
         <v>2.0843202273803882</v>
       </c>
       <c r="O51" s="1">
-        <v>0.48491154001112791</v>
+        <v>0.4849115400111278</v>
       </c>
       <c r="P51" s="1">
         <v>0.79004984454903038</v>
@@ -5966,10 +6782,10 @@
         <v>44.969999999999999</v>
       </c>
       <c r="S51" s="1">
-        <v>2160528267.2317109</v>
+        <v>1448059628.0364325</v>
       </c>
       <c r="T51" s="1">
-        <v>3.8973433034284737</v>
+        <v>3.8973433034284728</v>
       </c>
       <c r="U51" s="1">
         <v>2.395682609498464</v>
@@ -5980,25 +6796,25 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B52" t="s">
-        <v>599</v>
+        <v>871</v>
       </c>
       <c r="C52" t="s">
-        <v>654</v>
+        <v>926</v>
       </c>
       <c r="D52" t="s">
-        <v>709</v>
+        <v>981</v>
       </c>
       <c r="E52" t="s">
-        <v>764</v>
+        <v>1036</v>
       </c>
       <c r="F52" s="1">
         <v>38419000</v>
       </c>
       <c r="G52" s="1">
-        <v>3081029318.7697616</v>
+        <v>2065010783.2301726</v>
       </c>
       <c r="H52" s="1">
         <v>3420000</v>
@@ -6013,7 +6829,7 @@
         <v>1.3959183673469389</v>
       </c>
       <c r="L52" s="1">
-        <v>1.7837369286333442</v>
+        <v>1.7837369286333444</v>
       </c>
       <c r="M52" s="1">
         <v>1.5397082658022689</v>
@@ -6022,7 +6838,7 @@
         <v>1.6579819990525817</v>
       </c>
       <c r="O52" s="1">
-        <v>0.92949917246086677</v>
+        <v>0.92949917246086666</v>
       </c>
       <c r="P52" s="1">
         <v>1.0768156772794137</v>
@@ -6034,10 +6850,10 @@
         <v>46.869999999999997</v>
       </c>
       <c r="S52" s="1">
-        <v>896579558.20668733</v>
+        <v>600918155.64410996</v>
       </c>
       <c r="T52" s="1">
-        <v>1.617325905966932</v>
+        <v>1.6173259059669314</v>
       </c>
       <c r="U52" s="1">
         <v>1.3981628881373289</v>
@@ -6048,25 +6864,25 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B53" t="s">
-        <v>600</v>
+        <v>872</v>
       </c>
       <c r="C53" t="s">
-        <v>655</v>
+        <v>927</v>
       </c>
       <c r="D53" t="s">
-        <v>710</v>
+        <v>982</v>
       </c>
       <c r="E53" t="s">
-        <v>765</v>
+        <v>1037</v>
       </c>
       <c r="F53" s="1">
         <v>74937000</v>
       </c>
       <c r="G53" s="1">
-        <v>6009607070.9974127</v>
+        <v>4027843334.3637118</v>
       </c>
       <c r="H53" s="1">
         <v>5310000</v>
@@ -6081,7 +6897,7 @@
         <v>2.1673469387755104</v>
       </c>
       <c r="L53" s="1">
-        <v>3.4792132596110492</v>
+        <v>3.4792132596110505</v>
       </c>
       <c r="M53" s="1">
         <v>2.3905996758508916</v>
@@ -6090,7 +6906,7 @@
         <v>1.3895468182535922</v>
       </c>
       <c r="O53" s="1">
-        <v>0.39938535369025741</v>
+        <v>0.39938535369025724</v>
       </c>
       <c r="P53" s="1">
         <v>0.58125449956777375</v>
@@ -6102,10 +6918,10 @@
         <v>40.369999999999997</v>
       </c>
       <c r="S53" s="1">
-        <v>1117786941.7123554</v>
+        <v>749178877.95743501</v>
       </c>
       <c r="T53" s="1">
-        <v>2.0163584610370799</v>
+        <v>2.0163584610370795</v>
       </c>
       <c r="U53" s="1">
         <v>1.3875420008783141</v>
@@ -6116,25 +6932,25 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B54" t="s">
-        <v>601</v>
+        <v>873</v>
       </c>
       <c r="C54" t="s">
-        <v>656</v>
+        <v>928</v>
       </c>
       <c r="D54" t="s">
-        <v>711</v>
+        <v>983</v>
       </c>
       <c r="E54" t="s">
-        <v>766</v>
+        <v>1038</v>
       </c>
       <c r="F54" s="1">
         <v>58332000</v>
       </c>
       <c r="G54" s="1">
-        <v>4677961483.184823</v>
+        <v>3135329108.1855965</v>
       </c>
       <c r="H54" s="1">
         <v>3450000</v>
@@ -6149,7 +6965,7 @@
         <v>1.4081632653061225</v>
       </c>
       <c r="L54" s="1">
-        <v>2.7082678497889123</v>
+        <v>2.7082678497889132</v>
       </c>
       <c r="M54" s="1">
         <v>1.5532144786601836</v>
@@ -6158,7 +6974,7 @@
         <v>1.342175903994947</v>
       </c>
       <c r="O54" s="1">
-        <v>0.4955846239874534</v>
+        <v>0.49558462398745323</v>
       </c>
       <c r="P54" s="1">
         <v>0.86412786027639898</v>
@@ -6170,10 +6986,10 @@
         <v>53.130000000000003</v>
       </c>
       <c r="S54" s="1">
-        <v>1487591699.2330661</v>
+        <v>997034621.26954627</v>
       </c>
       <c r="T54" s="1">
-        <v>2.6834435055415042</v>
+        <v>2.6834435055415033</v>
       </c>
       <c r="U54" s="1">
         <v>1.5412917799882015</v>
@@ -6184,25 +7000,25 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>547</v>
+        <v>819</v>
       </c>
       <c r="B55" t="s">
-        <v>602</v>
+        <v>874</v>
       </c>
       <c r="C55" t="s">
-        <v>657</v>
+        <v>929</v>
       </c>
       <c r="D55" t="s">
-        <v>712</v>
+        <v>984</v>
       </c>
       <c r="E55" t="s">
-        <v>767</v>
+        <v>1039</v>
       </c>
       <c r="F55" s="1">
         <v>20672000</v>
       </c>
       <c r="G55" s="1">
-        <v>1657800517.3900547</v>
+        <v>1111114368.1754894</v>
       </c>
       <c r="H55" s="1">
         <v>1930000</v>
@@ -6217,7 +7033,7 @@
         <v>0.78775510204081634</v>
       </c>
       <c r="L55" s="1">
-        <v>0.95977016030371676</v>
+        <v>0.95977016030371687</v>
       </c>
       <c r="M55" s="1">
         <v>0.8688996938591752</v>
@@ -6226,7 +7042,7 @@
         <v>1.2474340754776567</v>
       </c>
       <c r="O55" s="1">
-        <v>1.2997216699078344</v>
+        <v>1.2997216699078342</v>
       </c>
       <c r="P55" s="1">
         <v>1.4356479629279644</v>
@@ -6238,10 +7054,10 @@
         <v>47.060000000000002</v>
       </c>
       <c r="S55" s="1">
-        <v>555363187.15943384</v>
+        <v>372223322.61064976</v>
       </c>
       <c r="T55" s="1">
-        <v>1.0018110067218959</v>
+        <v>1.0018110067218955</v>
       </c>
       <c r="U55" s="1">
         <v>0.90832399989933754</v>
@@ -6261,35 +7077,35 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>785</v>
+        <v>1057</v>
       </c>
       <c r="B1" t="s">
-        <v>813</v>
+        <v>1085</v>
       </c>
       <c r="C1" t="s">
-        <v>814</v>
+        <v>1086</v>
       </c>
       <c r="D1" t="s">
-        <v>815</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>786</v>
+        <v>1058</v>
       </c>
       <c r="B2" s="1">
-        <v>37.932246034579791</v>
+        <v>37.932246034579784</v>
       </c>
       <c r="C2" s="1">
         <v>36.393447308084603</v>
       </c>
       <c r="D2" s="1">
-        <v>35.247216919519545</v>
+        <v>35.247216919519552</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>787</v>
+        <v>1059</v>
       </c>
       <c r="B3" s="1">
         <v>24.888319876516452</v>
@@ -6303,7 +7119,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>788</v>
+        <v>1060</v>
       </c>
       <c r="B4" s="1">
         <v>23.598895859168564</v>
@@ -6317,21 +7133,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>789</v>
+        <v>1061</v>
       </c>
       <c r="B5" s="1">
-        <v>36.547405503038114</v>
+        <v>36.547405503038107</v>
       </c>
       <c r="C5" s="1">
-        <v>36.162651716146271</v>
+        <v>36.162651716146279</v>
       </c>
       <c r="D5" s="1">
-        <v>35.336122459164571</v>
+        <v>35.336122459164564</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>790</v>
+        <v>1062</v>
       </c>
       <c r="B6" s="1">
         <v>136.02453441661208</v>
@@ -6345,7 +7161,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>791</v>
+        <v>1063</v>
       </c>
       <c r="B7" s="1">
         <v>43.669072797610369</v>
@@ -6359,7 +7175,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>792</v>
+        <v>1064</v>
       </c>
       <c r="B8" s="1">
         <v>45.234299999999998</v>
@@ -6373,7 +7189,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>793</v>
+        <v>1065</v>
       </c>
       <c r="B9" s="1">
         <v>0.48314114809021386</v>
@@ -6382,12 +7198,12 @@
         <v>0.50732026587299228</v>
       </c>
       <c r="D9" s="1">
-        <v>0.50436956478105577</v>
+        <v>0.50436956478105555</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>794</v>
+        <v>1066</v>
       </c>
       <c r="B10" s="1">
         <v>0.74065035455682227</v>
@@ -6401,7 +7217,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>795</v>
+        <v>1067</v>
       </c>
       <c r="B11" s="1">
         <v>0.76296447286149527</v>
@@ -6415,13 +7231,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>796</v>
+        <v>1068</v>
       </c>
       <c r="B12" s="1">
-        <v>0.52636925307515814</v>
+        <v>0.52636925307515825</v>
       </c>
       <c r="C12" s="1">
-        <v>0.52754100084754507</v>
+        <v>0.52754100084754496</v>
       </c>
       <c r="D12" s="1">
         <v>0.52161876277301689</v>
@@ -6429,7 +7245,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>797</v>
+        <v>1069</v>
       </c>
       <c r="B13" s="1">
         <v>-0.27459274129392558</v>
@@ -6443,7 +7259,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>798</v>
+        <v>1070</v>
       </c>
       <c r="B14" s="1">
         <v>58.988200000000006</v>
@@ -6457,7 +7273,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>799</v>
+        <v>1071</v>
       </c>
       <c r="B15" s="1">
         <v>90.711228121495765</v>
@@ -6471,7 +7287,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>800</v>
+        <v>1072</v>
       </c>
       <c r="B16" s="1">
         <v>91.233653846153857</v>
@@ -6485,21 +7301,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>801</v>
+        <v>1073</v>
       </c>
       <c r="B17" s="1">
-        <v>-7.4014868308343773e-16</v>
+        <v>5.366077952354923e-16</v>
       </c>
       <c r="C17" s="1">
-        <v>1.1102230246251565e-16</v>
+        <v>9.0668213677721111e-16</v>
       </c>
       <c r="D17" s="1">
-        <v>-3.7007434154171883e-17</v>
+        <v>-1.7331814995537166e-15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>802</v>
+        <v>1074</v>
       </c>
       <c r="B18" s="1">
         <v>-7.8332402292997154e-16</v>
@@ -6513,7 +7329,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>803</v>
+        <v>1075</v>
       </c>
       <c r="B19" s="1">
         <v>-1.27675647831893e-15</v>
@@ -6527,21 +7343,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>804</v>
+        <v>1076</v>
       </c>
       <c r="B20" s="1">
-        <v>-1.30759600678074e-15</v>
+        <v>-1.6776703483224587e-15</v>
       </c>
       <c r="C20" s="1">
-        <v>-7.6482030585288566e-16</v>
+        <v>-1.8873791418627661e-15</v>
       </c>
       <c r="D20" s="1">
-        <v>-9.9920072216264089e-16</v>
+        <v>1.5296406117057713e-15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>805</v>
+        <v>1077</v>
       </c>
       <c r="B21" s="1">
         <v>14.272502230308012</v>
@@ -6555,21 +7371,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>806</v>
+        <v>1078</v>
       </c>
       <c r="B22" s="1">
-        <v>32.619620424953368</v>
+        <v>32.619620424953354</v>
       </c>
       <c r="C22" s="1">
-        <v>33.443607334390315</v>
+        <v>33.443607334390293</v>
       </c>
       <c r="D22" s="1">
-        <v>32.094178398256176</v>
+        <v>32.094178398256197</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>807</v>
+        <v>1079</v>
       </c>
       <c r="B23" s="1">
         <v>30.799999833106995</v>
@@ -6583,7 +7399,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>808</v>
+        <v>1080</v>
       </c>
       <c r="B24" s="1">
         <v>0.55830753353973173</v>
@@ -6597,7 +7413,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>809</v>
+        <v>1081</v>
       </c>
       <c r="B25" s="1">
         <v>0.86996904024767807</v>
@@ -6611,7 +7427,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>810</v>
+        <v>1082</v>
       </c>
       <c r="B26" s="1">
         <v>0.83075335397316818</v>
@@ -6625,7 +7441,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>811</v>
+        <v>1083</v>
       </c>
       <c r="B27" s="1">
         <v>0.66976264189886481</v>
@@ -6639,7 +7455,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>812</v>
+        <v>1084</v>
       </c>
       <c r="B28" s="1">
         <v>-0.29824561403508776</v>
